--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2020_metropolitana.xlsx
@@ -174,12 +174,15 @@
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
@@ -189,9 +192,6 @@
     <t xml:space="preserve">Las Condes</t>
   </si>
   <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:33</t>
+    <t xml:space="preserve">2026-09-10 00:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1413,7 +1413,7 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13108</v>
+        <v>13123</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -1426,7 +1426,7 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13123</v>
+        <v>13120</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1439,7 +1439,7 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13101</v>
+        <v>13108</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -1452,7 +1452,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13106</v>
+        <v>13101</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -1465,7 +1465,7 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13114</v>
+        <v>13106</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -1478,7 +1478,7 @@
         <v>57</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>13120</v>
+        <v>13114</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:40</t>
+    <t xml:space="preserve">2026-09-18 10:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
